--- a/output/Tables/Modal shift/HIA_modal_shift_1000replicate.xlsx
+++ b/output/Tables/Modal shift/HIA_modal_shift_1000replicate.xlsx
@@ -428,22 +428,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>24811.089</v>
+        <v>24807.52</v>
       </c>
       <c r="C2">
-        <v>22259.494</v>
+        <v>22251.611</v>
       </c>
       <c r="D2">
-        <v>27587.634</v>
+        <v>27581.024</v>
       </c>
       <c r="E2">
-        <v>261329.953</v>
+        <v>261368.914</v>
       </c>
       <c r="F2">
-        <v>246297.62</v>
+        <v>246355.981</v>
       </c>
       <c r="G2">
-        <v>277157.271</v>
+        <v>277033.261</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -455,13 +455,13 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>34757538900.523</v>
+        <v>34761187084.652</v>
       </c>
       <c r="L2">
-        <v>32742815667.168</v>
+        <v>32757016493.76</v>
       </c>
       <c r="M2">
-        <v>36850081790.897</v>
+        <v>36847319905.926</v>
       </c>
     </row>
     <row r="3">
@@ -471,40 +471,40 @@
         </is>
       </c>
       <c r="B3">
-        <v>14844.254</v>
+        <v>14870.291</v>
       </c>
       <c r="C3">
-        <v>13654.361</v>
+        <v>13669.857</v>
       </c>
       <c r="D3">
-        <v>16091.541</v>
+        <v>16132.648</v>
       </c>
       <c r="E3">
-        <v>13305.955</v>
+        <v>13333.848</v>
       </c>
       <c r="F3">
-        <v>12372.298</v>
+        <v>12394.295</v>
       </c>
       <c r="G3">
-        <v>14287.93</v>
+        <v>14310.299</v>
       </c>
       <c r="H3">
-        <v>826884749.176</v>
+        <v>828288934.8660001</v>
       </c>
       <c r="I3">
-        <v>760778742.76</v>
+        <v>761631293.763</v>
       </c>
       <c r="J3">
-        <v>896534488.469</v>
+        <v>898551876.142</v>
       </c>
       <c r="K3">
-        <v>1769680373.983</v>
+        <v>1773505283.773</v>
       </c>
       <c r="L3">
-        <v>1645566232.901</v>
+        <v>1648662413.414</v>
       </c>
       <c r="M3">
-        <v>1900358576.904</v>
+        <v>1902931586.378</v>
       </c>
     </row>
     <row r="4">
@@ -514,40 +514,40 @@
         </is>
       </c>
       <c r="B4">
-        <v>9792.941000000001</v>
+        <v>9800.971</v>
       </c>
       <c r="C4">
-        <v>9153.282999999999</v>
+        <v>9171.710999999999</v>
       </c>
       <c r="D4">
-        <v>10462.898</v>
+        <v>10470.168</v>
       </c>
       <c r="E4">
-        <v>15018.62</v>
+        <v>15041.028</v>
       </c>
       <c r="F4">
-        <v>13731.988</v>
+        <v>13769.296</v>
       </c>
       <c r="G4">
-        <v>16380.415</v>
+        <v>16399.699</v>
       </c>
       <c r="H4">
-        <v>145024112.503</v>
+        <v>145133798.126</v>
       </c>
       <c r="I4">
-        <v>135543734.3</v>
+        <v>135770207.903</v>
       </c>
       <c r="J4">
-        <v>154925104.608</v>
+        <v>155041456.583</v>
       </c>
       <c r="K4">
-        <v>1997152440.366</v>
+        <v>2000651956.892</v>
       </c>
       <c r="L4">
-        <v>1826510218.73</v>
+        <v>1831921392.131</v>
       </c>
       <c r="M4">
-        <v>2178654217.571</v>
+        <v>2179408996.831</v>
       </c>
     </row>
     <row r="5">
@@ -557,40 +557,40 @@
         </is>
       </c>
       <c r="B5">
-        <v>1931.696</v>
+        <v>1934.903</v>
       </c>
       <c r="C5">
-        <v>1791.712</v>
+        <v>1794.205</v>
       </c>
       <c r="D5">
-        <v>2082.439</v>
+        <v>2083.717</v>
       </c>
       <c r="E5">
-        <v>3788.277</v>
+        <v>3790.552</v>
       </c>
       <c r="F5">
-        <v>3498.151</v>
+        <v>3499.626</v>
       </c>
       <c r="G5">
-        <v>4097.933</v>
+        <v>4099.669</v>
       </c>
       <c r="H5">
-        <v>145251817.923</v>
+        <v>145499336.434</v>
       </c>
       <c r="I5">
-        <v>134731800.93</v>
+        <v>134966633.89</v>
       </c>
       <c r="J5">
-        <v>156588556.803</v>
+        <v>156681898.918</v>
       </c>
       <c r="K5">
-        <v>503795647.427</v>
+        <v>504189025.391</v>
       </c>
       <c r="L5">
-        <v>465355773.729</v>
+        <v>465623823.232</v>
       </c>
       <c r="M5">
-        <v>544663720.635</v>
+        <v>544908339.373</v>
       </c>
     </row>
     <row r="6">
@@ -600,40 +600,40 @@
         </is>
       </c>
       <c r="B6">
-        <v>5141.526</v>
+        <v>5128.97</v>
       </c>
       <c r="C6">
-        <v>4545.47</v>
+        <v>4540.216</v>
       </c>
       <c r="D6">
-        <v>5786.995</v>
+        <v>5757.579</v>
       </c>
       <c r="E6">
-        <v>8544.026</v>
+        <v>8551.344999999999</v>
       </c>
       <c r="F6">
-        <v>7789.658</v>
+        <v>7802.127</v>
       </c>
       <c r="G6">
-        <v>9349.477999999999</v>
+        <v>9355.950999999999</v>
       </c>
       <c r="H6">
-        <v>86526319.675</v>
+        <v>86333469.81</v>
       </c>
       <c r="I6">
-        <v>76551035.74699999</v>
+        <v>76469491.553</v>
       </c>
       <c r="J6">
-        <v>97377091.65800001</v>
+        <v>96925005.233</v>
       </c>
       <c r="K6">
-        <v>1136068638.015</v>
+        <v>1137242453.94</v>
       </c>
       <c r="L6">
-        <v>1036274963.903</v>
+        <v>1037409634.211</v>
       </c>
       <c r="M6">
-        <v>1243509882.37</v>
+        <v>1244066250.978</v>
       </c>
     </row>
     <row r="7">
@@ -643,22 +643,22 @@
         </is>
       </c>
       <c r="B7">
-        <v>48176.744</v>
+        <v>39960.131</v>
       </c>
       <c r="C7">
-        <v>45470.683</v>
+        <v>37632.675</v>
       </c>
       <c r="D7">
-        <v>50987.828</v>
+        <v>42399.413</v>
       </c>
       <c r="E7">
-        <v>140006.21</v>
+        <v>12929.994</v>
       </c>
       <c r="F7">
-        <v>128576.017</v>
+        <v>11855.053</v>
       </c>
       <c r="G7">
-        <v>152060.524</v>
+        <v>14070.188</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -670,13 +670,13 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>18625626318.316</v>
+        <v>1719770795.549</v>
       </c>
       <c r="L7">
-        <v>17097278205.329</v>
+        <v>1577285236.608</v>
       </c>
       <c r="M7">
-        <v>20226976503.057</v>
+        <v>1871580521.38</v>
       </c>
     </row>
     <row r="8">
@@ -686,40 +686,40 @@
         </is>
       </c>
       <c r="B8">
-        <v>79887.16099999999</v>
+        <v>71695.266</v>
       </c>
       <c r="C8">
-        <v>74615.50899999999</v>
+        <v>66808.664</v>
       </c>
       <c r="D8">
-        <v>85411.701</v>
+        <v>76843.52499999999</v>
       </c>
       <c r="E8">
-        <v>180663.088</v>
+        <v>53646.767</v>
       </c>
       <c r="F8">
-        <v>165968.112</v>
+        <v>49320.397</v>
       </c>
       <c r="G8">
-        <v>196176.28</v>
+        <v>58235.806</v>
       </c>
       <c r="H8">
-        <v>1203686999.277</v>
+        <v>1205255539.236</v>
       </c>
       <c r="I8">
-        <v>1107605313.737</v>
+        <v>1108837627.109</v>
       </c>
       <c r="J8">
-        <v>1305425241.538</v>
+        <v>1307200236.876</v>
       </c>
       <c r="K8">
-        <v>24032323418.107</v>
+        <v>7135359515.545</v>
       </c>
       <c r="L8">
-        <v>22070985394.592</v>
+        <v>6560902499.596</v>
       </c>
       <c r="M8">
-        <v>26094162900.537</v>
+        <v>7742895694.94</v>
       </c>
     </row>
     <row r="9">
@@ -729,40 +729,40 @@
         </is>
       </c>
       <c r="B9">
-        <v>104698.25</v>
+        <v>96502.78599999999</v>
       </c>
       <c r="C9">
-        <v>96875.003</v>
+        <v>89060.27500000001</v>
       </c>
       <c r="D9">
-        <v>112999.335</v>
+        <v>104424.549</v>
       </c>
       <c r="E9">
-        <v>441993.041</v>
+        <v>315015.681</v>
       </c>
       <c r="F9">
-        <v>412265.732</v>
+        <v>295676.378</v>
       </c>
       <c r="G9">
-        <v>473333.551</v>
+        <v>335269.067</v>
       </c>
       <c r="H9">
-        <v>1203686999.277</v>
+        <v>1205255539.236</v>
       </c>
       <c r="I9">
-        <v>1107605313.737</v>
+        <v>1108837627.109</v>
       </c>
       <c r="J9">
-        <v>1305425241.538</v>
+        <v>1307200236.876</v>
       </c>
       <c r="K9">
-        <v>58789862318.63</v>
+        <v>41896546600.19701</v>
       </c>
       <c r="L9">
-        <v>54813801061.76</v>
+        <v>39317918993.356</v>
       </c>
       <c r="M9">
-        <v>62944244691.43401</v>
+        <v>44590215600.866</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/Modal shift/HIA_modal_shift_1000replicate.xlsx
+++ b/output/Tables/Modal shift/HIA_modal_shift_1000replicate.xlsx
@@ -428,22 +428,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>24807.52</v>
+        <v>70260.22199999999</v>
       </c>
       <c r="C2">
-        <v>22251.611</v>
+        <v>66839.965</v>
       </c>
       <c r="D2">
-        <v>27581.024</v>
+        <v>73733.47</v>
       </c>
       <c r="E2">
-        <v>261368.914</v>
+        <v>721697.3540000001</v>
       </c>
       <c r="F2">
-        <v>246355.981</v>
+        <v>701749.254</v>
       </c>
       <c r="G2">
-        <v>277033.261</v>
+        <v>741853.598</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -455,13 +455,13 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>34761187084.652</v>
+        <v>95987464634.645</v>
       </c>
       <c r="L2">
-        <v>32757016493.76</v>
+        <v>93321277608.866</v>
       </c>
       <c r="M2">
-        <v>36847319905.926</v>
+        <v>98669601429.259</v>
       </c>
     </row>
     <row r="3">
@@ -471,40 +471,40 @@
         </is>
       </c>
       <c r="B3">
-        <v>14870.291</v>
+        <v>49984.755</v>
       </c>
       <c r="C3">
-        <v>13669.857</v>
+        <v>47909.553</v>
       </c>
       <c r="D3">
-        <v>16132.648</v>
+        <v>52072.543</v>
       </c>
       <c r="E3">
-        <v>13333.848</v>
+        <v>44514.578</v>
       </c>
       <c r="F3">
-        <v>12394.295</v>
+        <v>42883.609</v>
       </c>
       <c r="G3">
-        <v>14310.299</v>
+        <v>46161.146</v>
       </c>
       <c r="H3">
-        <v>828288934.8660001</v>
+        <v>2784145627.795</v>
       </c>
       <c r="I3">
-        <v>761631293.763</v>
+        <v>2669448027.564</v>
       </c>
       <c r="J3">
-        <v>898551876.142</v>
+        <v>2900844361.373</v>
       </c>
       <c r="K3">
-        <v>1773505283.773</v>
+        <v>5920537410.025</v>
       </c>
       <c r="L3">
-        <v>1648662413.414</v>
+        <v>5704047167.013</v>
       </c>
       <c r="M3">
-        <v>1902931586.378</v>
+        <v>6139271854.86</v>
       </c>
     </row>
     <row r="4">
@@ -514,40 +514,40 @@
         </is>
       </c>
       <c r="B4">
-        <v>9800.971</v>
+        <v>39862.819</v>
       </c>
       <c r="C4">
-        <v>9171.710999999999</v>
+        <v>38155.058</v>
       </c>
       <c r="D4">
-        <v>10470.168</v>
+        <v>41645.54</v>
       </c>
       <c r="E4">
-        <v>15041.028</v>
+        <v>60143.258</v>
       </c>
       <c r="F4">
-        <v>13769.296</v>
+        <v>56929.584</v>
       </c>
       <c r="G4">
-        <v>16399.699</v>
+        <v>63529.945</v>
       </c>
       <c r="H4">
-        <v>145133798.126</v>
+        <v>590301912.054</v>
       </c>
       <c r="I4">
-        <v>135770207.903</v>
+        <v>564946582.209</v>
       </c>
       <c r="J4">
-        <v>155041456.583</v>
+        <v>616730584.483</v>
       </c>
       <c r="K4">
-        <v>2000651956.892</v>
+        <v>7998322532.3</v>
       </c>
       <c r="L4">
-        <v>1831921392.131</v>
+        <v>7575713037.753</v>
       </c>
       <c r="M4">
-        <v>2179408996.831</v>
+        <v>8446470737.272</v>
       </c>
     </row>
     <row r="5">
@@ -557,40 +557,40 @@
         </is>
       </c>
       <c r="B5">
-        <v>1934.903</v>
+        <v>8147.487</v>
       </c>
       <c r="C5">
-        <v>1794.205</v>
+        <v>7782.849</v>
       </c>
       <c r="D5">
-        <v>2083.717</v>
+        <v>8517.870000000001</v>
       </c>
       <c r="E5">
-        <v>3790.552</v>
+        <v>15903.828</v>
       </c>
       <c r="F5">
-        <v>3499.626</v>
+        <v>15159.56</v>
       </c>
       <c r="G5">
-        <v>4099.669</v>
+        <v>16660.239</v>
       </c>
       <c r="H5">
-        <v>145499336.434</v>
+        <v>612629014.364</v>
       </c>
       <c r="I5">
-        <v>134966633.89</v>
+        <v>585296207.8559999</v>
       </c>
       <c r="J5">
-        <v>156681898.918</v>
+        <v>640545143.771</v>
       </c>
       <c r="K5">
-        <v>504189025.391</v>
+        <v>2114873938.014</v>
       </c>
       <c r="L5">
-        <v>465623823.232</v>
+        <v>2015940343.019</v>
       </c>
       <c r="M5">
-        <v>544908339.373</v>
+        <v>2216145255.823</v>
       </c>
     </row>
     <row r="6">
@@ -600,40 +600,40 @@
         </is>
       </c>
       <c r="B6">
-        <v>5128.97</v>
+        <v>17395.733</v>
       </c>
       <c r="C6">
-        <v>4540.216</v>
+        <v>16372.675</v>
       </c>
       <c r="D6">
-        <v>5757.579</v>
+        <v>18435.812</v>
       </c>
       <c r="E6">
-        <v>8551.344999999999</v>
+        <v>28772.697</v>
       </c>
       <c r="F6">
-        <v>7802.127</v>
+        <v>27434.328</v>
       </c>
       <c r="G6">
-        <v>9355.950999999999</v>
+        <v>30128.328</v>
       </c>
       <c r="H6">
-        <v>86333469.81</v>
+        <v>292841250.345</v>
       </c>
       <c r="I6">
-        <v>76469491.553</v>
+        <v>275756213.165</v>
       </c>
       <c r="J6">
-        <v>96925005.233</v>
+        <v>310201915.849</v>
       </c>
       <c r="K6">
-        <v>1137242453.94</v>
+        <v>3826289156.688</v>
       </c>
       <c r="L6">
-        <v>1037409634.211</v>
+        <v>3647639911.61</v>
       </c>
       <c r="M6">
-        <v>1244066250.978</v>
+        <v>4007473453.992</v>
       </c>
     </row>
     <row r="7">
@@ -643,22 +643,22 @@
         </is>
       </c>
       <c r="B7">
-        <v>39960.131</v>
+        <v>159354.564</v>
       </c>
       <c r="C7">
-        <v>37632.675</v>
+        <v>153824.632</v>
       </c>
       <c r="D7">
-        <v>42399.413</v>
+        <v>164980.434</v>
       </c>
       <c r="E7">
-        <v>12929.994</v>
+        <v>51671.99</v>
       </c>
       <c r="F7">
-        <v>11855.053</v>
+        <v>49208.513</v>
       </c>
       <c r="G7">
-        <v>14070.188</v>
+        <v>54217.087</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -670,13 +670,13 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>1719770795.549</v>
+        <v>6872861983.775</v>
       </c>
       <c r="L7">
-        <v>1577285236.608</v>
+        <v>6543556287.365</v>
       </c>
       <c r="M7">
-        <v>1871580521.38</v>
+        <v>7212584245.005</v>
       </c>
     </row>
     <row r="8">
@@ -686,40 +686,40 @@
         </is>
       </c>
       <c r="B8">
-        <v>71695.266</v>
+        <v>274745.358</v>
       </c>
       <c r="C8">
-        <v>66808.664</v>
+        <v>264044.767</v>
       </c>
       <c r="D8">
-        <v>76843.52499999999</v>
+        <v>285652.199</v>
       </c>
       <c r="E8">
-        <v>53646.767</v>
+        <v>201006.351</v>
       </c>
       <c r="F8">
-        <v>49320.397</v>
+        <v>191615.594</v>
       </c>
       <c r="G8">
-        <v>58235.806</v>
+        <v>210696.745</v>
       </c>
       <c r="H8">
-        <v>1205255539.236</v>
+        <v>4279917804.558</v>
       </c>
       <c r="I8">
-        <v>1108837627.109</v>
+        <v>4095447030.794</v>
       </c>
       <c r="J8">
-        <v>1307200236.876</v>
+        <v>4468322005.476</v>
       </c>
       <c r="K8">
-        <v>7135359515.545</v>
+        <v>26732885020.802</v>
       </c>
       <c r="L8">
-        <v>6560902499.596</v>
+        <v>25486896746.76</v>
       </c>
       <c r="M8">
-        <v>7742895694.94</v>
+        <v>28021945546.952</v>
       </c>
     </row>
     <row r="9">
@@ -729,40 +729,40 @@
         </is>
       </c>
       <c r="B9">
-        <v>96502.78599999999</v>
+        <v>345005.58</v>
       </c>
       <c r="C9">
-        <v>89060.27500000001</v>
+        <v>330884.732</v>
       </c>
       <c r="D9">
-        <v>104424.549</v>
+        <v>359385.669</v>
       </c>
       <c r="E9">
-        <v>315015.681</v>
+        <v>922703.7050000001</v>
       </c>
       <c r="F9">
-        <v>295676.378</v>
+        <v>893364.848</v>
       </c>
       <c r="G9">
-        <v>335269.067</v>
+        <v>952550.3429999999</v>
       </c>
       <c r="H9">
-        <v>1205255539.236</v>
+        <v>4279917804.558</v>
       </c>
       <c r="I9">
-        <v>1108837627.109</v>
+        <v>4095447030.794</v>
       </c>
       <c r="J9">
-        <v>1307200236.876</v>
+        <v>4468322005.476</v>
       </c>
       <c r="K9">
-        <v>41896546600.19701</v>
+        <v>122720349655.447</v>
       </c>
       <c r="L9">
-        <v>39317918993.356</v>
+        <v>118808174355.626</v>
       </c>
       <c r="M9">
-        <v>44590215600.866</v>
+        <v>126691546976.211</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/Modal shift/HIA_modal_shift_1000replicate.xlsx
+++ b/output/Tables/Modal shift/HIA_modal_shift_1000replicate.xlsx
@@ -1,21 +1,108 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/Modal shift/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EC463D9-89CA-9B41-91F6-DBF9CAE04131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+  <si>
+    <t>disease</t>
+  </si>
+  <si>
+    <t>tot_cases</t>
+  </si>
+  <si>
+    <t>tot_cases_low</t>
+  </si>
+  <si>
+    <t>tot_cases_up</t>
+  </si>
+  <si>
+    <t>tot_daly</t>
+  </si>
+  <si>
+    <t>tot_daly_low</t>
+  </si>
+  <si>
+    <t>tot_daly_up</t>
+  </si>
+  <si>
+    <t>tot_medic_costs</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_low</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_up</t>
+  </si>
+  <si>
+    <t>tot_soc_costs</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_low</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_up</t>
+  </si>
+  <si>
+    <t>mort</t>
+  </si>
+  <si>
+    <t>cvd</t>
+  </si>
+  <si>
+    <t>cancer</t>
+  </si>
+  <si>
+    <t>diab2</t>
+  </si>
+  <si>
+    <t>dem</t>
+  </si>
+  <si>
+    <t>dep</t>
+  </si>
+  <si>
+    <t>Morbidity</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +150,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +202,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +236,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +271,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,97 +447,80 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_low</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_up</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_low</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_up</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_low</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_up</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_low</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_up</t>
-        </is>
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>13</v>
       </c>
       <c r="B2">
-        <v>70260.22199999999</v>
+        <v>70260.221999999994</v>
       </c>
       <c r="C2">
-        <v>66839.965</v>
+        <v>66839.964999999997</v>
       </c>
       <c r="D2">
         <v>73733.47</v>
       </c>
       <c r="E2">
-        <v>721697.3540000001</v>
+        <v>721697.35400000005</v>
       </c>
       <c r="F2">
-        <v>701749.254</v>
+        <v>701749.25399999996</v>
       </c>
       <c r="G2">
         <v>741853.598</v>
@@ -455,115 +535,109 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>95987464634.645</v>
+        <v>95987464634.645004</v>
       </c>
       <c r="L2">
-        <v>93321277608.866</v>
+        <v>93321277608.865997</v>
       </c>
       <c r="M2">
-        <v>98669601429.259</v>
+        <v>98669601429.259003</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>14</v>
       </c>
       <c r="B3">
-        <v>49984.755</v>
+        <v>49984.754999999997</v>
       </c>
       <c r="C3">
         <v>47909.553</v>
       </c>
       <c r="D3">
-        <v>52072.543</v>
+        <v>52072.542999999998</v>
       </c>
       <c r="E3">
-        <v>44514.578</v>
+        <v>44514.578000000001</v>
       </c>
       <c r="F3">
-        <v>42883.609</v>
+        <v>42883.608999999997</v>
       </c>
       <c r="G3">
-        <v>46161.146</v>
+        <v>46161.146000000001</v>
       </c>
       <c r="H3">
-        <v>2784145627.795</v>
+        <v>2784145627.7950001</v>
       </c>
       <c r="I3">
-        <v>2669448027.564</v>
+        <v>2669448027.5640001</v>
       </c>
       <c r="J3">
-        <v>2900844361.373</v>
+        <v>2900844361.3730001</v>
       </c>
       <c r="K3">
-        <v>5920537410.025</v>
+        <v>5920537410.0249996</v>
       </c>
       <c r="L3">
-        <v>5704047167.013</v>
+        <v>5704047167.0129995</v>
       </c>
       <c r="M3">
-        <v>6139271854.86</v>
+        <v>6139271854.8599997</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>15</v>
       </c>
       <c r="B4">
-        <v>39862.819</v>
+        <v>39862.819000000003</v>
       </c>
       <c r="C4">
-        <v>38155.058</v>
+        <v>38155.057999999997</v>
       </c>
       <c r="D4">
         <v>41645.54</v>
       </c>
       <c r="E4">
-        <v>60143.258</v>
+        <v>60143.258000000002</v>
       </c>
       <c r="F4">
-        <v>56929.584</v>
+        <v>56929.584000000003</v>
       </c>
       <c r="G4">
         <v>63529.945</v>
       </c>
       <c r="H4">
-        <v>590301912.054</v>
+        <v>590301912.05400002</v>
       </c>
       <c r="I4">
-        <v>564946582.209</v>
+        <v>564946582.20899999</v>
       </c>
       <c r="J4">
-        <v>616730584.483</v>
+        <v>616730584.48300004</v>
       </c>
       <c r="K4">
-        <v>7998322532.3</v>
+        <v>7998322532.3000002</v>
       </c>
       <c r="L4">
-        <v>7575713037.753</v>
+        <v>7575713037.7530003</v>
       </c>
       <c r="M4">
-        <v>8446470737.272</v>
+        <v>8446470737.2720003</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>16</v>
       </c>
       <c r="B5">
-        <v>8147.487</v>
+        <v>8147.4870000000001</v>
       </c>
       <c r="C5">
-        <v>7782.849</v>
+        <v>7782.8490000000002</v>
       </c>
       <c r="D5">
-        <v>8517.870000000001</v>
+        <v>8517.8700000000008</v>
       </c>
       <c r="E5">
         <v>15903.828</v>
@@ -572,90 +646,86 @@
         <v>15159.56</v>
       </c>
       <c r="G5">
-        <v>16660.239</v>
+        <v>16660.239000000001</v>
       </c>
       <c r="H5">
-        <v>612629014.364</v>
+        <v>612629014.36399996</v>
       </c>
       <c r="I5">
-        <v>585296207.8559999</v>
+        <v>585296207.85599995</v>
       </c>
       <c r="J5">
-        <v>640545143.771</v>
+        <v>640545143.77100003</v>
       </c>
       <c r="K5">
-        <v>2114873938.014</v>
+        <v>2114873938.0139999</v>
       </c>
       <c r="L5">
-        <v>2015940343.019</v>
+        <v>2015940343.0190001</v>
       </c>
       <c r="M5">
         <v>2216145255.823</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>17</v>
       </c>
       <c r="B6">
         <v>17395.733</v>
       </c>
       <c r="C6">
-        <v>16372.675</v>
+        <v>16372.674999999999</v>
       </c>
       <c r="D6">
-        <v>18435.812</v>
+        <v>18435.812000000002</v>
       </c>
       <c r="E6">
         <v>28772.697</v>
       </c>
       <c r="F6">
-        <v>27434.328</v>
+        <v>27434.328000000001</v>
       </c>
       <c r="G6">
-        <v>30128.328</v>
+        <v>30128.328000000001</v>
       </c>
       <c r="H6">
-        <v>292841250.345</v>
+        <v>292841250.34500003</v>
       </c>
       <c r="I6">
-        <v>275756213.165</v>
+        <v>275756213.16500002</v>
       </c>
       <c r="J6">
-        <v>310201915.849</v>
+        <v>310201915.84899998</v>
       </c>
       <c r="K6">
-        <v>3826289156.688</v>
+        <v>3826289156.6880002</v>
       </c>
       <c r="L6">
-        <v>3647639911.61</v>
+        <v>3647639911.6100001</v>
       </c>
       <c r="M6">
-        <v>4007473453.992</v>
+        <v>4007473453.9920001</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>18</v>
       </c>
       <c r="B7">
-        <v>159354.564</v>
+        <v>159354.56400000001</v>
       </c>
       <c r="C7">
-        <v>153824.632</v>
+        <v>153824.63200000001</v>
       </c>
       <c r="D7">
-        <v>164980.434</v>
+        <v>164980.43400000001</v>
       </c>
       <c r="E7">
         <v>51671.99</v>
       </c>
       <c r="F7">
-        <v>49208.513</v>
+        <v>49208.512999999999</v>
       </c>
       <c r="G7">
         <v>54217.087</v>
@@ -670,96 +740,92 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>6872861983.775</v>
+        <v>6872861983.7749996</v>
       </c>
       <c r="L7">
-        <v>6543556287.365</v>
+        <v>6543556287.3649998</v>
       </c>
       <c r="M7">
-        <v>7212584245.005</v>
+        <v>7212584245.0050001</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Morbidity</t>
-        </is>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>19</v>
       </c>
       <c r="B8">
-        <v>274745.358</v>
+        <v>274745.35800000001</v>
       </c>
       <c r="C8">
-        <v>264044.767</v>
+        <v>264044.76699999999</v>
       </c>
       <c r="D8">
-        <v>285652.199</v>
+        <v>285652.19900000002</v>
       </c>
       <c r="E8">
         <v>201006.351</v>
       </c>
       <c r="F8">
-        <v>191615.594</v>
+        <v>191615.59400000001</v>
       </c>
       <c r="G8">
         <v>210696.745</v>
       </c>
       <c r="H8">
-        <v>4279917804.558</v>
+        <v>4279917804.5580001</v>
       </c>
       <c r="I8">
-        <v>4095447030.794</v>
+        <v>4095447030.7940001</v>
       </c>
       <c r="J8">
-        <v>4468322005.476</v>
+        <v>4468322005.4759998</v>
       </c>
       <c r="K8">
-        <v>26732885020.802</v>
+        <v>26732885020.801998</v>
       </c>
       <c r="L8">
-        <v>25486896746.76</v>
+        <v>25486896746.759998</v>
       </c>
       <c r="M8">
         <v>28021945546.952</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>20</v>
       </c>
       <c r="B9">
         <v>345005.58</v>
       </c>
       <c r="C9">
-        <v>330884.732</v>
+        <v>330884.73200000002</v>
       </c>
       <c r="D9">
-        <v>359385.669</v>
+        <v>359385.66899999999</v>
       </c>
       <c r="E9">
-        <v>922703.7050000001</v>
+        <v>922703.70500000007</v>
       </c>
       <c r="F9">
         <v>893364.848</v>
       </c>
       <c r="G9">
-        <v>952550.3429999999</v>
+        <v>952550.34299999988</v>
       </c>
       <c r="H9">
-        <v>4279917804.558</v>
+        <v>4279917804.5580001</v>
       </c>
       <c r="I9">
-        <v>4095447030.794</v>
+        <v>4095447030.7940001</v>
       </c>
       <c r="J9">
-        <v>4468322005.476</v>
+        <v>4468322005.4759998</v>
       </c>
       <c r="K9">
-        <v>122720349655.447</v>
+        <v>122720349655.44701</v>
       </c>
       <c r="L9">
-        <v>118808174355.626</v>
+        <v>118808174355.62601</v>
       </c>
       <c r="M9">
         <v>126691546976.211</v>
